--- a/asignaturas/fisica/propuesta/Propuesta_Fisica_G10-G11.xlsx
+++ b/asignaturas/fisica/propuesta/Propuesta_Fisica_G10-G11.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Fotón y efecto fotoeléctrico (11.°) e Interferencia de la luz (11.° tras la acción 1) de Dualidad onda-partícula, confianza alta; indicador vigente de 16.7: «Reconoce la predictibilidad de la trayectoria de la luz al incidir en un objeto»</t>
+          <t>prerrequisito: Fotón y efecto fotoeléctrico (11.° en Física, 15.4) e Interferencia de la luz (11.° tras la acción 1) de Dualidad onda-partícula, confianza alta; indicador vigente de 16.7: «Reconoce la predictibilidad de la trayectoria de la luz al incidir en un objeto»</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>CO 4, SG 5 (Conductores y aislantes eléctricos; candidato a mover a 10.°, sin bloqueos); prerrequisito: Conductores y aislantes eléctricos (11.°) de Circuito eléctrico simple (6.°), confianza alta</t>
+          <t>CO 4.5, SG 5 (Conductores y aislantes eléctricos; candidato a mover a 10.°, sin bloqueos); prerrequisito: Conductores y aislantes eléctricos (11.°) de Circuito eléctrico simple (6.°), confianza alta</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>No se mueve a 10.°: allí no hay electricidad y el retraso está en primaria (CO 4, SG 5). Las propuestas de 2.°–4.° y 5.°–8.° ya introducen la idea; en 11.° se explica con un modelo microscópico.</t>
+          <t>No se mueve a 10.°: allí no hay electricidad y el retraso está en la educación básica (CO 4.5, SG 5). Las propuestas de 2.°–4.° y 5.°–8.° ya introducen la idea; en 11.° se explica con un modelo microscópico.</t>
         </is>
       </c>
     </row>
@@ -961,6 +961,114 @@
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>La unidad 23 repite la relatividad de la unidad 19 y la radiación de la unidad 21. Reagrupar evita la repetición. Las métricas y el cálculo con Heisenberg superan TA15; integrar liberaría dos o tres sesiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>G10-FIS-U13-13.3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13. Transferencia de calor</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13.3. Aplicación de las leyes de Stefan-Boltzmann y de Wien a cuerpos calientes, e introducción cualitativa a la hipótesis de Planck sobre la cuantización de la energía.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Calcula la potencia radiada y la longitud de onda de máxima emisión de un cuerpo caliente, y explica con la hipótesis de Planck (E = hf) por qué la energía de la radiación se emite en paquetes.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Radiación térmica y cuerpo negro, Cuantización de la energía</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>prerrequisito: Cuantización de la energía (11.°, G11 15.3) de Fotón y efecto fotoeléctrico (10.°, por el tema de espectros de emisión de Química G10 3.5), confianza alta; prerrequisito: Radiación térmica y cuerpo negro (10.°, este tema) de Cuantización de la energía, confianza alta; TA-O2.2 Dualidad onda-partícula; efecto fotoeléctrico</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>El fotón aparece en 10.° en Química (espectros de emisión), pero la cuantización llega en 11.°. El cuerpo negro ya se estudia en 10.°: cerrar 13.3 con la hipótesis de Planck adelanta la idea sin costo. G11 15.3 la formaliza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>G10-FIS-U5-5.6</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>5. Las leyes de Newton</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>5.6. Clasificación de las fuerzas en las cuatro interacciones fundamentales (gravitatoria, electromagnética, nuclear fuerte y nuclear débil) y en fuerzas de contacto, y su identificación en situaciones reales.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Clasifica las fuerzas de situaciones cotidianas como de contacto o a distancia y las asocia a una de las cuatro interacciones fundamentales, sin recurrir a las partículas que las transmiten.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Fuerzas de contacto y a distancia, Fuerzas mecánicas comunes</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>prerrequisito: Núcleo atómico e isótopos (11.°, G11 20.1 y 20.2) de Modelo estándar de partículas (10.°, por la etiqueta secundaria de G10 5.6), confianza alta; tema principal del modelo estándar: G11 20.5, después de 20.1 y 20.2</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>5.6 nombra las interacciones fundamentales, no el modelo estándar de partículas. Se acota a ese nivel y se retira esa etiqueta. El modelo estándar queda en 11.° (20.5), después del núcleo; la arista es correcta.</t>
         </is>
       </c>
     </row>
